--- a/output/pdf_financials_xlsx/OBE.xlsx
+++ b/output/pdf_financials_xlsx/OBE.xlsx
@@ -2426,31 +2426,31 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>7.3e-06</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.000000000000001e-07</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5e-07</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0</v>
@@ -2536,31 +2536,31 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>7.3e-06</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.000000000000001e-07</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5e-07</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0</v>
@@ -3196,31 +3196,31 @@
         <v>0.000441</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000228</v>
+        <v>0.000161</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000151</v>
+        <v>0.000149</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.000228</v>
+        <v>0.000217</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.4e-05</v>
+        <v>8.2e-05</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.3e-05</v>
+        <v>2.1e-05</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.000107</v>
+        <v>0.000106</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.819999999999999e-05</v>
+        <v>1.089999999999999e-05</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.77e-05</v>
+        <v>1.69e-05</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.459999999999999e-05</v>
+        <v>2.409999999999999e-05</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.0004041</v>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/output/pdf_financials_xlsx/OBE.xlsx
+++ b/output/pdf_financials_xlsx/OBE.xlsx
@@ -1302,10 +1302,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-522</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.001009</v>
@@ -1362,16 +1360,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>378</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.000101</v>
+        <v>319</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.000227</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.000992</v>
+        <v>-5.8e-05</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0.000233</v>
@@ -1590,10 +1588,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-144</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>0.00111</v>
@@ -1602,7 +1598,7 @@
         <v>0.000638</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.000809</v>
+        <v>0.000125</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.000809</v>
@@ -1759,10 +1755,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-144</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0.00111</v>
@@ -1771,7 +1765,7 @@
         <v>0.000638</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.000809</v>
+        <v>0.000125</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.000809</v>
@@ -1952,7 +1946,7 @@
         <v>0.000469</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.002186</v>
+        <v>0.000338</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>0.000484</v>
@@ -2001,10 +1995,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-522</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0.001009</v>
@@ -2115,10 +2107,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-522</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.002178</v>
@@ -2174,10 +2164,8 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-22.08121827411167</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>8.68074930251096e-05</v>
@@ -2259,19 +2247,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-72.41379310344827</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>10.00991080277502</v>
+        <v>31615460.85232904</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>55.23114355231144</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>542.0765027322404</v>
+        <v>31.69398907103825</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-22.36084452975048</v>
@@ -2318,10 +2304,8 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>-6.091370558375635</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>4.424073335990434e-05</v>
@@ -6077,10 +6061,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-144</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>0.00111</v>
@@ -6089,7 +6071,7 @@
         <v>0.000638</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.000809</v>
+        <v>0.000125</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.000809</v>
@@ -6104,10 +6086,10 @@
         <v>-0.000696</v>
       </c>
       <c r="J99" s="3" t="n">
+        <v>-8.4e-05</v>
+      </c>
+      <c r="K99" s="3" t="n">
         <v>-0.000305</v>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>-0.000788</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-0.000788</v>
@@ -6726,25 +6708,25 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>4.5e-05</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>5.4e-05</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>4.3e-05</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>3.6e-05</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>3.7e-05</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -7411,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-4.74e-05</v>
       </c>
       <c r="P121" s="1" t="inlineStr">
         <is>
@@ -7499,42 +7481,40 @@
         <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>-0.000496</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>-0.000351</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>-0.000403</v>
       </c>
       <c r="H123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>-0.000133</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>-7.6e-05</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>8.4e-05</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>6.2e-05</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0</v>
+        <v>-7.35e-05</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>0</v>
+        <v>-0.0002165</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.5e-06</v>
+      </c>
+      <c r="P123" s="3" t="n">
+        <v>0.0001175</v>
       </c>
       <c r="Q123" s="1" t="inlineStr">
         <is>
@@ -7617,42 +7597,40 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000496</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000351</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000403</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000133</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-7.6e-05</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>8.4e-05</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>6.2e-05</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-7.35e-05</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0002165</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.5e-06</v>
+      </c>
+      <c r="P125" s="3" t="n">
+        <v>0.0001175</v>
       </c>
       <c r="Q125" s="1" t="inlineStr">
         <is>
@@ -7846,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>0</v>
+        <v>-4.7e-06</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>0</v>
+        <v>-6.5e-06</v>
       </c>
       <c r="O128" s="3" t="n">
-        <v>0</v>
+        <v>-8.000000000000001e-07</v>
       </c>
       <c r="P128" s="1" t="inlineStr">
         <is>
@@ -28772,7 +28750,11 @@
           <t>Increase in long-term debt 6</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -30858,7 +30840,11 @@
           <t>Deferred income tax expense (recovery) 10</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -32428,7 +32414,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -32710,7 +32700,11 @@
           <t>Repurchase of common shares 11</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -34304,7 +34298,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -34400,7 +34398,11 @@
           <t>Financing fees paid 5</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -34592,7 +34594,11 @@
           <t>Decrease in long-term debt 5</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -34876,7 +34882,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -36594,7 +36604,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E300" s="5" t="n">
         <v>-144</v>
       </c>
@@ -38272,7 +38286,11 @@
           <t>Increase in long-term debt 7</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -39698,7 +39716,11 @@
           <t>Deferred tax recovery 11</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -42418,7 +42440,11 @@
           <t>Decrease in long-term debt 8</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -43738,7 +43764,11 @@
           <t>Accretion 10</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -43830,7 +43860,11 @@
           <t>Deferred tax recovery 12</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -47206,7 +47240,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -47294,7 +47332,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -47570,7 +47612,11 @@
           <t>Decrease in long-term debt</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -49284,7 +49330,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -54980,7 +55030,11 @@
           <t>Future income tax recovery (note 11)</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E495" s="5" t="n">
         <v>-378</v>
       </c>
@@ -62038,7 +62092,11 @@
           <t>Deferred income tax (recovery) 10</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E571" t="inlineStr">
         <is>
           <t>-</t>
@@ -72780,7 +72838,11 @@
           <t>Future income tax recovery (note 11)</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E686" s="5" t="n">
         <v>-378</v>
       </c>
